--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -413,991 +413,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="C1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Measured by operator 7 on tool HRM-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Max Stepheight</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Min Stepheight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Mean Stepheight</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>16.62308</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.22002</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.55426</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.41688</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.82237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.72694</v>
+        <v>16.91927</v>
       </c>
       <c r="D3" t="n">
-        <v>16.88692</v>
+        <v>16.10784</v>
       </c>
       <c r="E3" t="n">
-        <v>16.49751</v>
+        <v>16.67164</v>
       </c>
       <c r="F3" t="n">
-        <v>41.76251</v>
+        <v>42.47287</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04954</v>
+        <v>0.05082</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80394</v>
+        <v>1.81723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81032</v>
+        <v>16.6801</v>
       </c>
       <c r="D4" t="n">
-        <v>16.74796</v>
+        <v>16.24438</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67654</v>
+        <v>16.27641</v>
       </c>
       <c r="F4" t="n">
-        <v>41.94717</v>
+        <v>42.93363</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04987</v>
+        <v>0.04971</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77521</v>
+        <v>1.76948</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.84735</v>
+        <v>16.40893</v>
       </c>
       <c r="D5" t="n">
-        <v>16.44301</v>
+        <v>16.28303</v>
       </c>
       <c r="E5" t="n">
-        <v>16.66564</v>
+        <v>16.38648</v>
       </c>
       <c r="F5" t="n">
-        <v>43.4296</v>
+        <v>41.47026</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04995</v>
+        <v>0.05029</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82159</v>
+        <v>1.83428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.50567</v>
+        <v>16.78165</v>
       </c>
       <c r="D6" t="n">
-        <v>16.58465</v>
+        <v>16.40603</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5501</v>
+        <v>16.48512</v>
       </c>
       <c r="F6" t="n">
-        <v>42.69</v>
+        <v>42.22471</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0504</v>
+        <v>0.05085</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8254</v>
+        <v>1.80291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.97825</v>
+        <v>16.95951</v>
       </c>
       <c r="D7" t="n">
-        <v>16.27617</v>
+        <v>16.37552</v>
       </c>
       <c r="E7" t="n">
-        <v>16.53828</v>
+        <v>16.4383</v>
       </c>
       <c r="F7" t="n">
-        <v>42.56109</v>
+        <v>42.98173</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05088</v>
+        <v>0.05002</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84669</v>
+        <v>1.84122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.547</v>
+        <v>16.75073</v>
       </c>
       <c r="D8" t="n">
-        <v>16.62628</v>
+        <v>16.60098</v>
       </c>
       <c r="E8" t="n">
-        <v>16.39369</v>
+        <v>16.64684</v>
       </c>
       <c r="F8" t="n">
-        <v>42.00857</v>
+        <v>42.70513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05006</v>
+        <v>0.04987</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78744</v>
+        <v>1.8089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.9361</v>
+        <v>16.71766</v>
       </c>
       <c r="D9" t="n">
-        <v>16.1486</v>
+        <v>16.456</v>
       </c>
       <c r="E9" t="n">
-        <v>16.43437</v>
+        <v>16.51274</v>
       </c>
       <c r="F9" t="n">
-        <v>41.56325</v>
+        <v>42.76569</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0502</v>
+        <v>0.0511</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80071</v>
+        <v>1.81293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.15434</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.48878</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.04946</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.36269</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05028</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.80787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>16.54658</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16.78757</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.53323</v>
-      </c>
-      <c r="F10" t="n">
-        <v>42.04907</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.79427</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>16.93204</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.58113</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.90941</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.233</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04994</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.84409</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>17.02368</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16.51576</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.22286</v>
-      </c>
-      <c r="F12" t="n">
-        <v>42.29278</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.04934</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.81846</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.54635</v>
+        <v>0.61617</v>
       </c>
       <c r="D13" t="n">
-        <v>16.25206</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.58972</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42.39211</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05056</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.79824</v>
+        <v>1.10326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.91898</v>
+        <v>0.60575</v>
       </c>
       <c r="D14" t="n">
-        <v>16.5236</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.66822</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.10475</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05024</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.86089</v>
+        <v>1.10134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.33197</v>
+        <v>0.62054</v>
       </c>
       <c r="D15" t="n">
-        <v>16.58853</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.50033</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.17946</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.04922</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.81328</v>
+        <v>1.09519</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.69267</v>
+        <v>0.59833</v>
       </c>
       <c r="D16" t="n">
-        <v>16.27344</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.47219</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.39675</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.04995</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.7762</v>
+        <v>1.09646</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.65445</v>
+        <v>0.60009</v>
       </c>
       <c r="D17" t="n">
-        <v>16.28927</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.72725</v>
-      </c>
-      <c r="F17" t="n">
-        <v>41.94995</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.04933</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.83424</v>
+        <v>1.12005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.86947</v>
+        <v>0.6080100000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>16.45659</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.58656</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.38159</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.04933</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.80026</v>
+        <v>1.11527</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.03053</v>
+        <v>0.60411</v>
       </c>
       <c r="D19" t="n">
-        <v>16.26838</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.45647</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.16393</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05069</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.8234</v>
+        <v>1.10853</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.59844</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.09255</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>16.57999</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.3322</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.75184</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.34581</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.04999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.80851</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="C21" t="n">
+        <v>0.60446</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.10618</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.6210599999999999</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.11132</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.59289</v>
+        <v>0.74669</v>
       </c>
       <c r="D23" t="n">
-        <v>1.08655</v>
+        <v>0.07915999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.59632</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.96818</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.10766</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09347</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.12514</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.60287</v>
+        <v>0.73811</v>
       </c>
       <c r="D24" t="n">
-        <v>1.10558</v>
+        <v>0.08137</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.95429</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1091</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09143999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.12815</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.59971</v>
+        <v>0.74286</v>
       </c>
       <c r="D25" t="n">
-        <v>1.11028</v>
+        <v>0.08044</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.61627</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.93581</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09418</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.12845</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6067900000000001</v>
+        <v>0.7419</v>
       </c>
       <c r="D26" t="n">
-        <v>1.08295</v>
+        <v>0.08311</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.60207</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.10802</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09486</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.12818</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.59933</v>
+        <v>0.75842</v>
       </c>
       <c r="D27" t="n">
-        <v>1.09057</v>
+        <v>0.08079</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.60802</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.93046</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.10928</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.09251</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.12213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.60769</v>
+        <v>0.7426</v>
       </c>
       <c r="D28" t="n">
-        <v>1.089</v>
+        <v>0.08075</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.61463</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.97041</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.10898</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09322</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.59444</v>
+        <v>0.73297</v>
       </c>
       <c r="D29" t="n">
-        <v>1.10984</v>
+        <v>0.07990999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.59962</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9356</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.10753</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09332</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.12637</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.73568</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08022</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.60346</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.96706</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.10639</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09476999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1238</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.61787</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.11364</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.7353499999999999</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.08076</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.6138400000000001</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.96749</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.10738</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09354</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12582</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.76069</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.07897999999999999</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.59832</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.95984</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.10827</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09163</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.12458</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.74982</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.07976</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.61696</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.95044</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.10742</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09493</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.12512</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.72895</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.08099000000000001</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.60351</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.96031</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.1085</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09299</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.12651</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.75642</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.08001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.60761</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.95217</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.11168</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09363</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.12746</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.74969</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.07994</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.59776</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.94694</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.10846</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09248000000000001</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.12721</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.7507</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.08065</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.60706</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.95034</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.10915</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00736</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.12471</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.7571600000000001</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.07961</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.61249</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.94454</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.10883</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09358</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.12335</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.74343</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.08037999999999999</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.60271</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.9454</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.10822</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.09467</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12738</v>
+      <c r="C31" t="n">
+        <v>0.73733</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08066</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.59989</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.93927</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10882</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09087000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12678</v>
       </c>
     </row>
   </sheetData>
